--- a/marketer_forms/008_social_media_marketing_quiz--marketer_forms.xlsx
+++ b/marketer_forms/008_social_media_marketing_quiz--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>marketing_goal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>social_media_channel</t>
+          <t>preferred_channel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>correct_answer_1</t>
+          <t>usage_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the primary goal of social media marketing?</t>
+          <t>How often do you use social media?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>correct_answer_2</t>
+          <t>knowledge_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which social media channel do you prefer?</t>
+          <t>What is your current level of knowledge in marketing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>correct_answer_3</t>
+          <t>correct_answer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you use social media?</t>
+          <t>What is the correct answer about social media marketing?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>marketing_goal</t>
+          <t>actual_channel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your current level of knowledge in marketing?</t>
+          <t>Which social media channel do you actually use?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>correct_answer_4</t>
+          <t>actual_answer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the primary goal of social media marketing?</t>
+          <t>Actual Answer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>correct_answer_5</t>
+          <t>actual_usage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which social media channel do you prefer?</t>
+          <t>How often do you actually use social media?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,85 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>correct_answer_6</t>
+          <t>final_answer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the correct answer about social media marketing?</t>
+          <t>Final Answer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>correct_answer_7</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>How often do you use social media?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>correct_answer_8</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>What is the correct answer about social media marketing?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>correct_answer_9</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Which social media channel do you use?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
@@ -850,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>marketing_goal_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -867,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>marketing_goal_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -884,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>marketing_goal_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>social_media_channel_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>social_media_channel_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>social_media_channel_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>social_media_channel_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,177 +900,177 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>correct_answer_1_choices</t>
+          <t>knowledge_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>social_media_marketing</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Social Media Marketing</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>correct_answer_1_choices</t>
+          <t>knowledge_level_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>online_advertising</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Online Advertising</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>correct_answer_1_choices</t>
+          <t>knowledge_level_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>social_media_management</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Social Media Management</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>correct_answer_2_choices</t>
+          <t>correct_answer_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>social_media_marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Social Media Marketing</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>correct_answer_2_choices</t>
+          <t>correct_answer_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>correct_answer_2_choices</t>
+          <t>correct_answer_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>social_media_management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Social Media Management</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>correct_answer_2_choices</t>
+          <t>actual_channel_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>marketing_goal_choices</t>
+          <t>actual_channel_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>marketing_goal_choices</t>
+          <t>actual_channel_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>marketing_goal_choices</t>
+          <t>actual_channel_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>correct_answer_4_choices</t>
+          <t>actual_answer_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1156,7 +1087,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>correct_answer_4_choices</t>
+          <t>actual_answer_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1173,7 +1104,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>correct_answer_4_choices</t>
+          <t>actual_answer_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1190,238 +1121,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>correct_answer_5_choices</t>
+          <t>final_answer_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>social_media_marketing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Social Media Marketing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>correct_answer_5_choices</t>
+          <t>final_answer_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>correct_answer_5_choices</t>
+          <t>final_answer_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>social_media_management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>correct_answer_5_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>correct_answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>social_media_marketing</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Social Media Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>correct_answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>online_advertising</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Online Advertising</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>correct_answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>social_media_management</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>Social Media Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>correct_answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>social_media_marketing</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Social Media Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>correct_answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>online_advertising</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Online Advertising</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>correct_answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>social_media_management</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Social Media Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>correct_answer_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>correct_answer_9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>twitter</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Twitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>correct_answer_9_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>correct_answer_9_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>YouTube</t>
         </is>
       </c>
     </row>
